--- a/docs/package/05_Delivery/Upload_Templates/Vehicle_Model_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Vehicle_Model_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
   <si>
     <t xml:space="preserve">Brand</t>
   </si>
@@ -93,12 +93,6 @@
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle (choose Vehicle models in the Upload dialog) &gt; Upload</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/masters/vehicle-model/upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -129,10 +123,10 @@
     <t xml:space="preserve">The rows under the header on the Data sheet are samples. Delete them before you upload your own data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dates and amounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter dates as YYYY-MM-DD and amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
+    <t xml:space="preserve">Amounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
   </si>
   <si>
     <t xml:space="preserve">What happens on errors</t>
@@ -150,10 +144,10 @@
     <t xml:space="preserve">Linked columns take the name (or code) of a record that already exists in the linked master; upload the linked master first.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -161,9 +155,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -190,8 +184,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -219,6 +247,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -250,9 +296,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -273,6 +319,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,7 +458,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -501,24 +554,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="4" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13">
       <c r="B13" s="4" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
